--- a/night_inline_task_with_skill_df_class.xlsx
+++ b/night_inline_task_with_skill_df_class.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,11 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>PreferGender</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>RequiredCount</t>
         </is>
       </c>
@@ -508,12 +513,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -528,22 +533,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BSFA13</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -553,12 +558,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>88</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>OJT3103-Testing OP</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -566,7 +571,12 @@
           <t>regular</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>M&amp;F</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -578,12 +588,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -598,22 +608,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BSFA13</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -623,12 +633,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ECU VI</t>
+          <t>OJT3124-Material Handling</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -636,77 +646,12 @@
           <t>regular</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ME/MOE6-CN</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ME/MFO6.5-CN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>BSFA13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>S122</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cluster_Service Entry</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>M&amp;F</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
     </row>

--- a/night_inline_task_with_skill_df_class.xlsx
+++ b/night_inline_task_with_skill_df_class.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,11 +496,6 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>PreferGender</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>RequiredCount</t>
         </is>
       </c>
@@ -571,12 +566,7 @@
           <t>regular</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>M&amp;F</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+      <c r="N2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -646,12 +636,7 @@
           <t>regular</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>M&amp;F</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
     </row>
